--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task068.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task068.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -559,6 +559,50 @@
         <v>5.1927213523744635</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>548</v>
+      </c>
+      <c r="B11" s="0">
+        <v>680</v>
+      </c>
+      <c r="C11" s="0">
+        <v>548</v>
+      </c>
+      <c r="D11" s="0">
+        <v>79.016935856845578</v>
+      </c>
+      <c r="E11" s="0">
+        <v>477.88</v>
+      </c>
+      <c r="F11" s="0">
+        <v>154.12152041001269</v>
+      </c>
+      <c r="G11" s="0">
+        <v>58181.348814258519</v>
+      </c>
+      <c r="H11" s="0">
+        <v>-8203.7153372767007</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5.9249999999999998</v>
+      </c>
+      <c r="J11" s="0">
+        <v>17.740000000000002</v>
+      </c>
+      <c r="K11" s="0">
+        <v>2.7600000000000007</v>
+      </c>
+      <c r="L11" s="0">
+        <v>3.8700000000000006</v>
+      </c>
+      <c r="M11" s="0">
+        <v>291.55593090213171</v>
+      </c>
+      <c r="N11" s="0">
+        <v>5.1927213523745408</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>